--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N28_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N28_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.95305613354382</v>
+        <v>2.59237162170087</v>
       </c>
       <c r="D2" t="n">
-        <v>23.22885416923041</v>
+        <v>3.774688802499941</v>
       </c>
       <c r="E2" t="n">
-        <v>8.604360982448387</v>
+        <v>1.398208659647863</v>
       </c>
       <c r="F2" t="n">
-        <v>5.244809982698222</v>
+        <v>0.852281622188461</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.7102867298452</v>
+        <v>2.552921593599846</v>
       </c>
       <c r="D3" t="n">
-        <v>13.72398930413883</v>
+        <v>2.230148261922559</v>
       </c>
       <c r="E3" t="n">
-        <v>8.604360982448387</v>
+        <v>1.398208659647863</v>
       </c>
       <c r="F3" t="n">
-        <v>5.244809982698222</v>
+        <v>0.852281622188461</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.429737951659</v>
+        <v>4.619832417144588</v>
       </c>
       <c r="D4" t="n">
-        <v>18.98277091124145</v>
+        <v>3.084700273076736</v>
       </c>
       <c r="E4" t="n">
-        <v>8.604360982448387</v>
+        <v>1.398208659647863</v>
       </c>
       <c r="F4" t="n">
-        <v>5.244809982698222</v>
+        <v>0.852281622188461</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>35.96016682497645</v>
+        <v>5.843527109058674</v>
       </c>
       <c r="D5" t="n">
-        <v>9.357939489285773</v>
+        <v>1.520665167008938</v>
       </c>
       <c r="E5" t="n">
-        <v>8.604360982448387</v>
+        <v>1.398208659647863</v>
       </c>
       <c r="F5" t="n">
-        <v>5.244809982698222</v>
+        <v>0.852281622188461</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
